--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEW_MEXICO_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEW_MEXICO_2023.xlsx
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C118">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C208">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C260">
